--- a/reports/pdf_change_20260922.xlsx
+++ b/reports/pdf_change_20260922.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,789억   ·   현금 26억(0.6%)      당일 2026-09-22  vs  전영업일 2026-09-21      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,789억      당일 2026-09-22  vs  전영업일 2026-09-21      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -795,7 +795,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,325억   ·   현금 59억(1.8%)      당일 2026-09-22  vs  전영업일 2026-09-21      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,325억      당일 2026-09-22  vs  전영업일 2026-09-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -819,7 +819,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,616억   ·   현금 43억(1.6%)      당일 2026-09-22  vs  전영업일 2026-09-21      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,616억      당일 2026-09-22  vs  전영업일 2026-09-21      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -843,7 +843,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,005억   ·   현금 15억(0.8%)      당일 2026-09-22  vs  전영업일 2026-09-21      매수 3종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,005억      당일 2026-09-22  vs  전영업일 2026-09-21      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1064,7 +1064,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억   ·   현금 1억(0.5%)      당일 2026-09-22  vs  전영업일 2026-09-21      매수 3종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 289억      당일 2026-09-22  vs  전영업일 2026-09-21      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
